--- a/Hoàng/SALE/BÁO GIÁ THAM KHẢO.xlsx
+++ b/Hoàng/SALE/BÁO GIÁ THAM KHẢO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\LÀM VIỆC\DATA_TN\Hoàng\SALE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\SALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6972BE12-D517-4E7F-9458-438666663734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9ECD085-186D-4A91-A9F1-0823D6F21153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5805" yWindow="3735" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BÁO GIÁ CHUNG" sheetId="4" r:id="rId1"/>
@@ -1335,7 +1335,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -1906,7 +1906,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2252,6 +2252,36 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2261,58 +2291,37 @@
     <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2321,9 +2330,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2333,15 +2339,15 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2357,6 +2363,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -2411,15 +2426,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2455,12 +2461,6 @@
     </xf>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2847,43 +2847,43 @@
       <c r="A1" s="22"/>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
-      <c r="D1" s="162" t="s">
+      <c r="D1" s="167" t="s">
         <v>312</v>
       </c>
-      <c r="E1" s="163"/>
-      <c r="F1" s="164"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="169"/>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="164"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="168"/>
+      <c r="F2" s="169"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="164"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="169"/>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="164"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="168"/>
+      <c r="F4" s="169"/>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="166"/>
-      <c r="F5" s="167"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="172"/>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
@@ -2894,14 +2894,14 @@
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="168" t="s">
+      <c r="A7" s="173" t="s">
         <v>419</v>
       </c>
-      <c r="B7" s="169"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="170"/>
+      <c r="B7" s="174"/>
+      <c r="C7" s="174"/>
+      <c r="D7" s="174"/>
+      <c r="E7" s="174"/>
+      <c r="F7" s="175"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -2923,27 +2923,27 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
-      <c r="B9" s="171" t="s">
+      <c r="B9" s="176" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="172"/>
-      <c r="D9" s="172"/>
-      <c r="E9" s="172"/>
-      <c r="F9" s="173"/>
+      <c r="C9" s="177"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="177"/>
+      <c r="F9" s="178"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="174" t="s">
+      <c r="A10" s="179" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="175"/>
-      <c r="C10" s="175"/>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="176"/>
+      <c r="B10" s="180"/>
+      <c r="C10" s="180"/>
+      <c r="D10" s="180"/>
+      <c r="E10" s="180"/>
+      <c r="F10" s="181"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -2951,12 +2951,12 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="177"/>
-      <c r="B11" s="178"/>
-      <c r="C11" s="178"/>
-      <c r="D11" s="178"/>
-      <c r="E11" s="178"/>
-      <c r="F11" s="179"/>
+      <c r="A11" s="182"/>
+      <c r="B11" s="183"/>
+      <c r="C11" s="183"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="183"/>
+      <c r="F11" s="184"/>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
       <c r="I11" s="21"/>
@@ -2975,10 +2975,10 @@
       <c r="A13" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="B13" s="183" t="s">
+      <c r="B13" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="183"/>
+      <c r="C13" s="185"/>
       <c r="D13" s="33" t="s">
         <v>3</v>
       </c>
@@ -2991,77 +2991,77 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="184">
+      <c r="A14" s="186">
         <v>1</v>
       </c>
-      <c r="B14" s="139" t="s">
+      <c r="B14" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="187" t="s">
+      <c r="C14" s="189" t="s">
         <v>327</v>
       </c>
       <c r="D14" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="137">
         <v>200000</v>
       </c>
-      <c r="F14" s="190"/>
+      <c r="F14" s="192"/>
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="185"/>
+      <c r="A15" s="187"/>
       <c r="B15" s="147"/>
-      <c r="C15" s="188"/>
+      <c r="C15" s="190"/>
       <c r="D15" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="128"/>
-      <c r="F15" s="191"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="193"/>
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.25">
-      <c r="A16" s="185"/>
+      <c r="A16" s="187"/>
       <c r="B16" s="147"/>
-      <c r="C16" s="188"/>
+      <c r="C16" s="190"/>
       <c r="D16" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="128"/>
-      <c r="F16" s="191"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="193"/>
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="185"/>
+      <c r="A17" s="187"/>
       <c r="B17" s="147"/>
-      <c r="C17" s="188"/>
+      <c r="C17" s="190"/>
       <c r="D17" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="128"/>
-      <c r="F17" s="191"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="193"/>
       <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="185"/>
+      <c r="A18" s="187"/>
       <c r="B18" s="147"/>
-      <c r="C18" s="188"/>
+      <c r="C18" s="190"/>
       <c r="D18" s="35" t="s">
         <v>412</v>
       </c>
-      <c r="E18" s="128"/>
-      <c r="F18" s="191"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="193"/>
       <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="186"/>
-      <c r="B19" s="140"/>
-      <c r="C19" s="189"/>
+      <c r="A19" s="188"/>
+      <c r="B19" s="148"/>
+      <c r="C19" s="191"/>
       <c r="D19" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="129"/>
-      <c r="F19" s="192"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="194"/>
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3144,7 +3144,7 @@
       <c r="A24" s="37">
         <v>6</v>
       </c>
-      <c r="B24" s="138" t="s">
+      <c r="B24" s="149" t="s">
         <v>40</v>
       </c>
       <c r="C24" s="41" t="s">
@@ -3153,10 +3153,10 @@
       <c r="D24" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="193">
+      <c r="E24" s="195">
         <v>60000</v>
       </c>
-      <c r="F24" s="157" t="s">
+      <c r="F24" s="159" t="s">
         <v>382</v>
       </c>
       <c r="G24" s="12"/>
@@ -3165,15 +3165,15 @@
       <c r="A25" s="37">
         <v>7</v>
       </c>
-      <c r="B25" s="138"/>
+      <c r="B25" s="149"/>
       <c r="C25" s="41" t="s">
         <v>43</v>
       </c>
       <c r="D25" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="194"/>
-      <c r="F25" s="158"/>
+      <c r="E25" s="196"/>
+      <c r="F25" s="160"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -3213,12 +3213,12 @@
       <c r="G27" s="12"/>
     </row>
     <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="180" t="s">
+      <c r="A28" s="164" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="182"/>
-      <c r="C28" s="182"/>
-      <c r="D28" s="181"/>
+      <c r="B28" s="166"/>
+      <c r="C28" s="166"/>
+      <c r="D28" s="165"/>
       <c r="E28" s="121">
         <f>SUM(E14:E27)</f>
         <v>564000</v>
@@ -3259,10 +3259,10 @@
       <c r="A32" s="61" t="s">
         <v>259</v>
       </c>
-      <c r="B32" s="180" t="s">
+      <c r="B32" s="164" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="181"/>
+      <c r="C32" s="165"/>
       <c r="D32" s="61" t="s">
         <v>3</v>
       </c>
@@ -3370,7 +3370,7 @@
         <f>IF(LEN(C38)=0,"",COUNTA($C$34:C38))</f>
         <v>5</v>
       </c>
-      <c r="B38" s="139" t="s">
+      <c r="B38" s="146" t="s">
         <v>44</v>
       </c>
       <c r="C38" s="41" t="s">
@@ -3392,7 +3392,7 @@
         <f>IF(LEN(C39)=0,"",COUNTA($C$34:C39))</f>
         <v>6</v>
       </c>
-      <c r="B39" s="140"/>
+      <c r="B39" s="148"/>
       <c r="C39" s="41" t="s">
         <v>274</v>
       </c>
@@ -3424,7 +3424,7 @@
       <c r="E40" s="69">
         <v>41000</v>
       </c>
-      <c r="F40" s="134" t="s">
+      <c r="F40" s="131" t="s">
         <v>378</v>
       </c>
       <c r="G40" s="12"/>
@@ -3444,7 +3444,7 @@
       <c r="E41" s="69">
         <v>59000</v>
       </c>
-      <c r="F41" s="135"/>
+      <c r="F41" s="132"/>
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3462,7 +3462,7 @@
       <c r="E42" s="69">
         <v>59000</v>
       </c>
-      <c r="F42" s="135"/>
+      <c r="F42" s="132"/>
       <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3480,7 +3480,7 @@
       <c r="E43" s="69">
         <v>47000</v>
       </c>
-      <c r="F43" s="135"/>
+      <c r="F43" s="132"/>
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3498,7 +3498,7 @@
       <c r="E44" s="69">
         <v>41000</v>
       </c>
-      <c r="F44" s="136"/>
+      <c r="F44" s="133"/>
       <c r="G44" s="12"/>
     </row>
     <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3526,7 +3526,7 @@
         <f>IF(LEN(C46)=0,"",COUNTA($C$34:C46))</f>
         <v>13</v>
       </c>
-      <c r="B46" s="139" t="s">
+      <c r="B46" s="146" t="s">
         <v>277</v>
       </c>
       <c r="C46" s="35" t="s">
@@ -3538,7 +3538,7 @@
       <c r="E46" s="72">
         <v>62000</v>
       </c>
-      <c r="F46" s="134" t="s">
+      <c r="F46" s="131" t="s">
         <v>379</v>
       </c>
       <c r="G46" s="12"/>
@@ -3558,7 +3558,7 @@
       <c r="E47" s="72">
         <v>165000</v>
       </c>
-      <c r="F47" s="135"/>
+      <c r="F47" s="132"/>
       <c r="G47" s="12"/>
     </row>
     <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3566,7 +3566,7 @@
         <f>IF(LEN(C48)=0,"",COUNTA($C$34:C48))</f>
         <v>15</v>
       </c>
-      <c r="B48" s="140"/>
+      <c r="B48" s="148"/>
       <c r="C48" s="35" t="s">
         <v>201</v>
       </c>
@@ -3576,7 +3576,7 @@
       <c r="E48" s="72">
         <v>116000</v>
       </c>
-      <c r="F48" s="136"/>
+      <c r="F48" s="133"/>
       <c r="G48" s="12"/>
     </row>
     <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3584,7 +3584,7 @@
         <f>IF(LEN(C49)=0,"",COUNTA($C$34:C49))</f>
         <v>16</v>
       </c>
-      <c r="B49" s="139" t="s">
+      <c r="B49" s="146" t="s">
         <v>272</v>
       </c>
       <c r="C49" s="35" t="s">
@@ -3614,7 +3614,7 @@
       <c r="E50" s="72">
         <v>130000</v>
       </c>
-      <c r="F50" s="134" t="s">
+      <c r="F50" s="131" t="s">
         <v>379</v>
       </c>
       <c r="G50" s="12"/>
@@ -3634,7 +3634,7 @@
       <c r="E51" s="72">
         <v>120000</v>
       </c>
-      <c r="F51" s="135"/>
+      <c r="F51" s="132"/>
       <c r="G51" s="12"/>
     </row>
     <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3642,7 +3642,7 @@
         <f>IF(LEN(C52)=0,"",COUNTA($C$34:C52))</f>
         <v>19</v>
       </c>
-      <c r="B52" s="140"/>
+      <c r="B52" s="148"/>
       <c r="C52" s="35" t="s">
         <v>271</v>
       </c>
@@ -3652,7 +3652,7 @@
       <c r="E52" s="72">
         <v>282000</v>
       </c>
-      <c r="F52" s="136"/>
+      <c r="F52" s="133"/>
       <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3680,7 +3680,7 @@
         <f>IF(LEN(C54)=0,"",COUNTA($C$34:C54))</f>
         <v>21</v>
       </c>
-      <c r="B54" s="143" t="s">
+      <c r="B54" s="140" t="s">
         <v>130</v>
       </c>
       <c r="C54" s="35" t="s">
@@ -3692,7 +3692,7 @@
       <c r="E54" s="72">
         <v>71000</v>
       </c>
-      <c r="F54" s="157" t="s">
+      <c r="F54" s="159" t="s">
         <v>381</v>
       </c>
       <c r="G54" s="12"/>
@@ -3702,7 +3702,7 @@
         <f>IF(LEN(C55)=0,"",COUNTA($C$34:C55))</f>
         <v>22</v>
       </c>
-      <c r="B55" s="145"/>
+      <c r="B55" s="141"/>
       <c r="C55" s="35" t="s">
         <v>133</v>
       </c>
@@ -3712,7 +3712,7 @@
       <c r="E55" s="68">
         <v>138000</v>
       </c>
-      <c r="F55" s="158"/>
+      <c r="F55" s="160"/>
       <c r="G55" s="12"/>
     </row>
     <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3740,7 +3740,7 @@
         <f>IF(LEN(C57)=0,"",COUNTA($C$34:C57))</f>
         <v>24</v>
       </c>
-      <c r="B57" s="159" t="s">
+      <c r="B57" s="161" t="s">
         <v>205</v>
       </c>
       <c r="C57" s="35" t="s">
@@ -3752,7 +3752,7 @@
       <c r="E57" s="72">
         <v>30000</v>
       </c>
-      <c r="F57" s="160" t="s">
+      <c r="F57" s="162" t="s">
         <v>383</v>
       </c>
       <c r="G57" s="13"/>
@@ -3762,7 +3762,7 @@
         <f>IF(LEN(C58)=0,"",COUNTA($C$34:C58))</f>
         <v>25</v>
       </c>
-      <c r="B58" s="159"/>
+      <c r="B58" s="161"/>
       <c r="C58" s="35" t="s">
         <v>278</v>
       </c>
@@ -3772,7 +3772,7 @@
       <c r="E58" s="72">
         <v>20000</v>
       </c>
-      <c r="F58" s="161"/>
+      <c r="F58" s="163"/>
       <c r="G58" s="13"/>
     </row>
     <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3811,7 +3811,7 @@
         <f>IF(LEN(C61)=0,"",COUNTA($C$34:C61))</f>
         <v>27</v>
       </c>
-      <c r="B61" s="148"/>
+      <c r="B61" s="151"/>
       <c r="C61" s="73" t="s">
         <v>83</v>
       </c>
@@ -3829,7 +3829,7 @@
         <f>IF(LEN(C62)=0,"",COUNTA($C$34:C62))</f>
         <v>28</v>
       </c>
-      <c r="B62" s="148"/>
+      <c r="B62" s="151"/>
       <c r="C62" s="73" t="s">
         <v>85</v>
       </c>
@@ -3847,7 +3847,7 @@
         <f>IF(LEN(C63)=0,"",COUNTA($C$34:C63))</f>
         <v>29</v>
       </c>
-      <c r="B63" s="148"/>
+      <c r="B63" s="151"/>
       <c r="C63" s="73" t="s">
         <v>79</v>
       </c>
@@ -3865,7 +3865,7 @@
         <f>IF(LEN(C64)=0,"",COUNTA($C$34:C64))</f>
         <v>30</v>
       </c>
-      <c r="B64" s="148"/>
+      <c r="B64" s="151"/>
       <c r="C64" s="73" t="s">
         <v>93</v>
       </c>
@@ -3883,7 +3883,7 @@
         <f>IF(LEN(C65)=0,"",COUNTA($C$34:C65))</f>
         <v>31</v>
       </c>
-      <c r="B65" s="148"/>
+      <c r="B65" s="151"/>
       <c r="C65" s="73" t="s">
         <v>80</v>
       </c>
@@ -3901,7 +3901,7 @@
         <f>IF(LEN(C66)=0,"",COUNTA($C$34:C66))</f>
         <v>32</v>
       </c>
-      <c r="B66" s="148"/>
+      <c r="B66" s="151"/>
       <c r="C66" s="73" t="s">
         <v>82</v>
       </c>
@@ -3921,7 +3921,7 @@
         <f>IF(LEN(C67)=0,"",COUNTA($C$34:C67))</f>
         <v>33</v>
       </c>
-      <c r="B67" s="148"/>
+      <c r="B67" s="151"/>
       <c r="C67" s="75" t="s">
         <v>234</v>
       </c>
@@ -3939,7 +3939,7 @@
         <f>IF(LEN(C68)=0,"",COUNTA($C$34:C68))</f>
         <v>34</v>
       </c>
-      <c r="B68" s="148"/>
+      <c r="B68" s="151"/>
       <c r="C68" s="73" t="s">
         <v>73</v>
       </c>
@@ -3959,7 +3959,7 @@
         <f>IF(LEN(C69)=0,"",COUNTA($C$34:C69))</f>
         <v>35</v>
       </c>
-      <c r="B69" s="148"/>
+      <c r="B69" s="151"/>
       <c r="C69" s="73" t="s">
         <v>75</v>
       </c>
@@ -3977,7 +3977,7 @@
         <f>IF(LEN(C70)=0,"",COUNTA($C$34:C70))</f>
         <v>36</v>
       </c>
-      <c r="B70" s="148"/>
+      <c r="B70" s="151"/>
       <c r="C70" s="73" t="s">
         <v>77</v>
       </c>
@@ -3995,7 +3995,7 @@
         <f>IF(LEN(C71)=0,"",COUNTA($C$34:C71))</f>
         <v>37</v>
       </c>
-      <c r="B71" s="148"/>
+      <c r="B71" s="151"/>
       <c r="C71" s="73" t="s">
         <v>87</v>
       </c>
@@ -4013,7 +4013,7 @@
         <f>IF(LEN(C72)=0,"",COUNTA($C$34:C72))</f>
         <v>38</v>
       </c>
-      <c r="B72" s="149"/>
+      <c r="B72" s="152"/>
       <c r="C72" s="73" t="s">
         <v>95</v>
       </c>
@@ -4037,13 +4037,13 @@
       <c r="C73" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="D73" s="151" t="s">
+      <c r="D73" s="153" t="s">
         <v>397</v>
       </c>
       <c r="E73" s="39">
         <v>137000</v>
       </c>
-      <c r="F73" s="134" t="s">
+      <c r="F73" s="131" t="s">
         <v>380</v>
       </c>
       <c r="G73" s="13"/>
@@ -4053,15 +4053,15 @@
         <f>IF(LEN(C74)=0,"",COUNTA($C$34:C74))</f>
         <v>40</v>
       </c>
-      <c r="B74" s="148"/>
+      <c r="B74" s="151"/>
       <c r="C74" s="73" t="s">
         <v>91</v>
       </c>
-      <c r="D74" s="152"/>
+      <c r="D74" s="154"/>
       <c r="E74" s="39">
         <v>137000</v>
       </c>
-      <c r="F74" s="135"/>
+      <c r="F74" s="132"/>
       <c r="G74" s="13"/>
     </row>
     <row r="75" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
@@ -4069,15 +4069,15 @@
         <f>IF(LEN(C75)=0,"",COUNTA($C$34:C75))</f>
         <v>41</v>
       </c>
-      <c r="B75" s="149"/>
+      <c r="B75" s="152"/>
       <c r="C75" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="D75" s="153"/>
+      <c r="D75" s="155"/>
       <c r="E75" s="39">
         <v>208000</v>
       </c>
-      <c r="F75" s="136"/>
+      <c r="F75" s="133"/>
       <c r="G75" s="13"/>
     </row>
     <row r="76" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4091,7 +4091,7 @@
       <c r="C76" s="73" t="s">
         <v>399</v>
       </c>
-      <c r="D76" s="154" t="s">
+      <c r="D76" s="157" t="s">
         <v>401</v>
       </c>
       <c r="E76" s="39">
@@ -4105,11 +4105,11 @@
         <f>IF(LEN(C77)=0,"",COUNTA($C$34:C77))</f>
         <v>43</v>
       </c>
-      <c r="B77" s="148"/>
+      <c r="B77" s="151"/>
       <c r="C77" s="73" t="s">
         <v>400</v>
       </c>
-      <c r="D77" s="155"/>
+      <c r="D77" s="158"/>
       <c r="E77" s="39">
         <v>323000</v>
       </c>
@@ -4121,7 +4121,7 @@
         <f>IF(LEN(C78)=0,"",COUNTA($C$34:C78))</f>
         <v>44</v>
       </c>
-      <c r="B78" s="148"/>
+      <c r="B78" s="151"/>
       <c r="C78" s="73" t="s">
         <v>403</v>
       </c>
@@ -4139,7 +4139,7 @@
         <f>IF(LEN(C79)=0,"",COUNTA($C$34:C79))</f>
         <v>45</v>
       </c>
-      <c r="B79" s="149"/>
+      <c r="B79" s="152"/>
       <c r="C79" s="73" t="s">
         <v>404</v>
       </c>
@@ -4153,12 +4153,12 @@
       <c r="G79" s="13"/>
     </row>
     <row r="80" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="130" t="s">
+      <c r="A80" s="134" t="s">
         <v>207</v>
       </c>
-      <c r="B80" s="131"/>
-      <c r="C80" s="131"/>
-      <c r="D80" s="132"/>
+      <c r="B80" s="135"/>
+      <c r="C80" s="135"/>
+      <c r="D80" s="136"/>
       <c r="E80" s="66"/>
       <c r="F80" s="67"/>
       <c r="G80" s="13"/>
@@ -4362,7 +4362,7 @@
         <f>IF(LEN(C91)=0,"",COUNTA($C$34:C91))</f>
         <v>56</v>
       </c>
-      <c r="B91" s="143" t="s">
+      <c r="B91" s="140" t="s">
         <v>121</v>
       </c>
       <c r="C91" s="35" t="s">
@@ -4382,7 +4382,7 @@
         <f>IF(LEN(C92)=0,"",COUNTA($C$34:C92))</f>
         <v>57</v>
       </c>
-      <c r="B92" s="144"/>
+      <c r="B92" s="142"/>
       <c r="C92" s="35" t="s">
         <v>389</v>
       </c>
@@ -4400,7 +4400,7 @@
         <f>IF(LEN(C93)=0,"",COUNTA($C$34:C93))</f>
         <v>58</v>
       </c>
-      <c r="B93" s="145"/>
+      <c r="B93" s="141"/>
       <c r="C93" s="35" t="s">
         <v>125</v>
       </c>
@@ -4414,12 +4414,12 @@
       <c r="G93" s="12"/>
     </row>
     <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="130" t="s">
+      <c r="A94" s="134" t="s">
         <v>261</v>
       </c>
-      <c r="B94" s="131"/>
-      <c r="C94" s="131"/>
-      <c r="D94" s="132"/>
+      <c r="B94" s="135"/>
+      <c r="C94" s="135"/>
+      <c r="D94" s="136"/>
       <c r="E94" s="77"/>
       <c r="F94" s="67"/>
       <c r="G94" s="12"/>
@@ -4429,7 +4429,7 @@
         <f>IF(LEN(C95)=0,"",COUNTA($C$34:C95))</f>
         <v>59</v>
       </c>
-      <c r="B95" s="139" t="s">
+      <c r="B95" s="146" t="s">
         <v>240</v>
       </c>
       <c r="C95" s="35" t="s">
@@ -4449,7 +4449,7 @@
         <f>IF(LEN(C96)=0,"",COUNTA($C$34:C96))</f>
         <v>60</v>
       </c>
-      <c r="B96" s="140"/>
+      <c r="B96" s="148"/>
       <c r="C96" s="35" t="s">
         <v>239</v>
       </c>
@@ -4467,7 +4467,7 @@
         <f>IF(LEN(C97)=0,"",COUNTA($C$34:C97))</f>
         <v>61</v>
       </c>
-      <c r="B97" s="143" t="s">
+      <c r="B97" s="140" t="s">
         <v>243</v>
       </c>
       <c r="C97" s="35" t="s">
@@ -4485,7 +4485,7 @@
         <f>IF(LEN(C98)=0,"",COUNTA($C$34:C98))</f>
         <v>62</v>
       </c>
-      <c r="B98" s="145"/>
+      <c r="B98" s="141"/>
       <c r="C98" s="35" t="s">
         <v>242</v>
       </c>
@@ -4521,7 +4521,7 @@
         <f>IF(LEN(C100)=0,"",COUNTA($C$34:C100))</f>
         <v>64</v>
       </c>
-      <c r="B100" s="143" t="s">
+      <c r="B100" s="140" t="s">
         <v>258</v>
       </c>
       <c r="C100" s="35" t="s">
@@ -4539,7 +4539,7 @@
         <f>IF(LEN(C101)=0,"",COUNTA($C$34:C101))</f>
         <v>65</v>
       </c>
-      <c r="B101" s="144"/>
+      <c r="B101" s="142"/>
       <c r="C101" s="35" t="s">
         <v>245</v>
       </c>
@@ -4555,7 +4555,7 @@
         <f>IF(LEN(C102)=0,"",COUNTA($C$34:C102))</f>
         <v>66</v>
       </c>
-      <c r="B102" s="144"/>
+      <c r="B102" s="142"/>
       <c r="C102" s="35" t="s">
         <v>246</v>
       </c>
@@ -4571,7 +4571,7 @@
         <f>IF(LEN(C103)=0,"",COUNTA($C$34:C103))</f>
         <v>67</v>
       </c>
-      <c r="B103" s="144"/>
+      <c r="B103" s="142"/>
       <c r="C103" s="35" t="s">
         <v>247</v>
       </c>
@@ -4587,7 +4587,7 @@
         <f>IF(LEN(C104)=0,"",COUNTA($C$34:C104))</f>
         <v>68</v>
       </c>
-      <c r="B104" s="144"/>
+      <c r="B104" s="142"/>
       <c r="C104" s="35" t="s">
         <v>248</v>
       </c>
@@ -4603,7 +4603,7 @@
         <f>IF(LEN(C105)=0,"",COUNTA($C$34:C105))</f>
         <v>69</v>
       </c>
-      <c r="B105" s="144"/>
+      <c r="B105" s="142"/>
       <c r="C105" s="35" t="s">
         <v>249</v>
       </c>
@@ -4619,7 +4619,7 @@
         <f>IF(LEN(C106)=0,"",COUNTA($C$34:C106))</f>
         <v>70</v>
       </c>
-      <c r="B106" s="144"/>
+      <c r="B106" s="142"/>
       <c r="C106" s="35" t="s">
         <v>250</v>
       </c>
@@ -4635,7 +4635,7 @@
         <f>IF(LEN(C107)=0,"",COUNTA($C$34:C107))</f>
         <v>71</v>
       </c>
-      <c r="B107" s="144"/>
+      <c r="B107" s="142"/>
       <c r="C107" s="35" t="s">
         <v>251</v>
       </c>
@@ -4651,7 +4651,7 @@
         <f>IF(LEN(C108)=0,"",COUNTA($C$34:C108))</f>
         <v>72</v>
       </c>
-      <c r="B108" s="144"/>
+      <c r="B108" s="142"/>
       <c r="C108" s="35" t="s">
         <v>252</v>
       </c>
@@ -4667,7 +4667,7 @@
         <f>IF(LEN(C109)=0,"",COUNTA($C$34:C109))</f>
         <v>73</v>
       </c>
-      <c r="B109" s="144"/>
+      <c r="B109" s="142"/>
       <c r="C109" s="35" t="s">
         <v>253</v>
       </c>
@@ -4683,7 +4683,7 @@
         <f>IF(LEN(C110)=0,"",COUNTA($C$34:C110))</f>
         <v>74</v>
       </c>
-      <c r="B110" s="144"/>
+      <c r="B110" s="142"/>
       <c r="C110" s="35" t="s">
         <v>254</v>
       </c>
@@ -4699,7 +4699,7 @@
         <f>IF(LEN(C111)=0,"",COUNTA($C$34:C111))</f>
         <v>75</v>
       </c>
-      <c r="B111" s="144"/>
+      <c r="B111" s="142"/>
       <c r="C111" s="35" t="s">
         <v>255</v>
       </c>
@@ -4715,7 +4715,7 @@
         <f>IF(LEN(C112)=0,"",COUNTA($C$34:C112))</f>
         <v>76</v>
       </c>
-      <c r="B112" s="144"/>
+      <c r="B112" s="142"/>
       <c r="C112" s="35" t="s">
         <v>256</v>
       </c>
@@ -4731,7 +4731,7 @@
         <f>IF(LEN(C113)=0,"",COUNTA($C$34:C113))</f>
         <v>77</v>
       </c>
-      <c r="B113" s="145"/>
+      <c r="B113" s="141"/>
       <c r="C113" s="35" t="s">
         <v>257</v>
       </c>
@@ -4743,12 +4743,12 @@
       <c r="G113" s="12"/>
     </row>
     <row r="114" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="130" t="s">
+      <c r="A114" s="134" t="s">
         <v>226</v>
       </c>
-      <c r="B114" s="131"/>
-      <c r="C114" s="131"/>
-      <c r="D114" s="132"/>
+      <c r="B114" s="135"/>
+      <c r="C114" s="135"/>
+      <c r="D114" s="136"/>
       <c r="E114" s="66"/>
       <c r="F114" s="67"/>
       <c r="G114" s="12"/>
@@ -4794,12 +4794,12 @@
       <c r="G116" s="12"/>
     </row>
     <row r="117" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="137" t="s">
+      <c r="A117" s="130" t="s">
         <v>262</v>
       </c>
-      <c r="B117" s="137"/>
-      <c r="C117" s="137"/>
-      <c r="D117" s="137"/>
+      <c r="B117" s="130"/>
+      <c r="C117" s="130"/>
+      <c r="D117" s="130"/>
       <c r="E117" s="77"/>
       <c r="F117" s="67"/>
       <c r="G117" s="12"/>
@@ -4809,7 +4809,7 @@
         <f>IF(LEN(C118)=0,"",COUNTA($C$34:C118))</f>
         <v>80</v>
       </c>
-      <c r="B118" s="195" t="s">
+      <c r="B118" s="143" t="s">
         <v>204</v>
       </c>
       <c r="C118" s="36" t="s">
@@ -4829,7 +4829,7 @@
         <f>IF(LEN(C119)=0,"",COUNTA($C$34:C119))</f>
         <v>81</v>
       </c>
-      <c r="B119" s="146"/>
+      <c r="B119" s="144"/>
       <c r="C119" s="36" t="s">
         <v>34</v>
       </c>
@@ -4847,7 +4847,7 @@
         <f>IF(LEN(C120)=0,"",COUNTA($C$34:C120))</f>
         <v>82</v>
       </c>
-      <c r="B120" s="146"/>
+      <c r="B120" s="144"/>
       <c r="C120" s="36" t="s">
         <v>325</v>
       </c>
@@ -4865,7 +4865,7 @@
         <f>IF(LEN(C121)=0,"",COUNTA($C$34:C121))</f>
         <v>83</v>
       </c>
-      <c r="B121" s="146"/>
+      <c r="B121" s="144"/>
       <c r="C121" s="35" t="s">
         <v>408</v>
       </c>
@@ -4881,7 +4881,7 @@
         <f>IF(LEN(C122)=0,"",COUNTA($C$34:C122))</f>
         <v>84</v>
       </c>
-      <c r="B122" s="146"/>
+      <c r="B122" s="144"/>
       <c r="C122" s="35" t="s">
         <v>409</v>
       </c>
@@ -4897,7 +4897,7 @@
         <f>IF(LEN(C123)=0,"",COUNTA($C$34:C123))</f>
         <v>85</v>
       </c>
-      <c r="B123" s="146"/>
+      <c r="B123" s="144"/>
       <c r="C123" s="35" t="s">
         <v>410</v>
       </c>
@@ -4913,7 +4913,7 @@
         <f>IF(LEN(C124)=0,"",COUNTA($C$34:C124))</f>
         <v>86</v>
       </c>
-      <c r="B124" s="146"/>
+      <c r="B124" s="144"/>
       <c r="C124" s="36" t="s">
         <v>411</v>
       </c>
@@ -4931,7 +4931,7 @@
         <f>IF(LEN(C125)=0,"",COUNTA($C$34:C125))</f>
         <v>87</v>
       </c>
-      <c r="B125" s="146"/>
+      <c r="B125" s="144"/>
       <c r="C125" s="36" t="s">
         <v>138</v>
       </c>
@@ -4949,7 +4949,7 @@
         <f>IF(LEN(C126)=0,"",COUNTA($C$34:C126))</f>
         <v>88</v>
       </c>
-      <c r="B126" s="196"/>
+      <c r="B126" s="145"/>
       <c r="C126" s="36" t="s">
         <v>139</v>
       </c>
@@ -4967,7 +4967,7 @@
         <f>IF(LEN(C127)=0,"",COUNTA($C$34:C127))</f>
         <v>89</v>
       </c>
-      <c r="B127" s="139" t="s">
+      <c r="B127" s="146" t="s">
         <v>282</v>
       </c>
       <c r="C127" s="35" t="s">
@@ -5059,7 +5059,7 @@
         <f>IF(LEN(C132)=0,"",COUNTA($C$34:C132))</f>
         <v>94</v>
       </c>
-      <c r="B132" s="140"/>
+      <c r="B132" s="148"/>
       <c r="C132" s="35" t="s">
         <v>145</v>
       </c>
@@ -5199,7 +5199,7 @@
         <f>IF(LEN(C140)=0,"",COUNTA($C$34:C140))</f>
         <v>102</v>
       </c>
-      <c r="B140" s="138" t="s">
+      <c r="B140" s="149" t="s">
         <v>304</v>
       </c>
       <c r="C140" s="35" t="s">
@@ -5221,7 +5221,7 @@
         <f>IF(LEN(C141)=0,"",COUNTA($C$34:C141))</f>
         <v>103</v>
       </c>
-      <c r="B141" s="138"/>
+      <c r="B141" s="149"/>
       <c r="C141" s="35" t="s">
         <v>343</v>
       </c>
@@ -5239,7 +5239,7 @@
         <f>IF(LEN(C142)=0,"",COUNTA($C$34:C142))</f>
         <v>104</v>
       </c>
-      <c r="B142" s="138"/>
+      <c r="B142" s="149"/>
       <c r="C142" s="35" t="s">
         <v>344</v>
       </c>
@@ -5259,7 +5259,7 @@
         <f>IF(LEN(C143)=0,"",COUNTA($C$34:C143))</f>
         <v>105</v>
       </c>
-      <c r="B143" s="138"/>
+      <c r="B143" s="149"/>
       <c r="C143" s="35" t="s">
         <v>345</v>
       </c>
@@ -5277,7 +5277,7 @@
         <f>IF(LEN(C144)=0,"",COUNTA($C$34:C144))</f>
         <v>106</v>
       </c>
-      <c r="B144" s="138"/>
+      <c r="B144" s="149"/>
       <c r="C144" s="35" t="s">
         <v>346</v>
       </c>
@@ -5295,7 +5295,7 @@
         <f>IF(LEN(C145)=0,"",COUNTA($C$34:C145))</f>
         <v>107</v>
       </c>
-      <c r="B145" s="138"/>
+      <c r="B145" s="149"/>
       <c r="C145" s="107" t="s">
         <v>373</v>
       </c>
@@ -5313,7 +5313,7 @@
         <f>IF(LEN(C146)=0,"",COUNTA($C$34:C146))</f>
         <v>108</v>
       </c>
-      <c r="B146" s="138"/>
+      <c r="B146" s="149"/>
       <c r="C146" s="35" t="s">
         <v>347</v>
       </c>
@@ -5331,7 +5331,7 @@
         <f>IF(LEN(C147)=0,"",COUNTA($C$34:C147))</f>
         <v>109</v>
       </c>
-      <c r="B147" s="138"/>
+      <c r="B147" s="149"/>
       <c r="C147" s="35" t="s">
         <v>348</v>
       </c>
@@ -5349,7 +5349,7 @@
         <f>IF(LEN(C148)=0,"",COUNTA($C$34:C148))</f>
         <v>110</v>
       </c>
-      <c r="B148" s="138"/>
+      <c r="B148" s="149"/>
       <c r="C148" s="35" t="s">
         <v>349</v>
       </c>
@@ -5367,7 +5367,7 @@
         <f>IF(LEN(C149)=0,"",COUNTA($C$34:C149))</f>
         <v>111</v>
       </c>
-      <c r="B149" s="138"/>
+      <c r="B149" s="149"/>
       <c r="C149" s="107" t="s">
         <v>372</v>
       </c>
@@ -5385,7 +5385,7 @@
         <f>IF(LEN(C150)=0,"",COUNTA($C$34:C150))</f>
         <v>112</v>
       </c>
-      <c r="B150" s="138"/>
+      <c r="B150" s="149"/>
       <c r="C150" s="35" t="s">
         <v>350</v>
       </c>
@@ -5405,7 +5405,7 @@
         <f>IF(LEN(C151)=0,"",COUNTA($C$34:C151))</f>
         <v>113</v>
       </c>
-      <c r="B151" s="138"/>
+      <c r="B151" s="149"/>
       <c r="C151" s="35" t="s">
         <v>351</v>
       </c>
@@ -5423,7 +5423,7 @@
         <f>IF(LEN(C152)=0,"",COUNTA($C$34:C152))</f>
         <v>114</v>
       </c>
-      <c r="B152" s="138"/>
+      <c r="B152" s="149"/>
       <c r="C152" s="35" t="s">
         <v>352</v>
       </c>
@@ -5441,7 +5441,7 @@
         <f>IF(LEN(C153)=0,"",COUNTA($C$34:C153))</f>
         <v>115</v>
       </c>
-      <c r="B153" s="138"/>
+      <c r="B153" s="149"/>
       <c r="C153" s="35" t="s">
         <v>353</v>
       </c>
@@ -5459,7 +5459,7 @@
         <f>IF(LEN(C154)=0,"",COUNTA($C$34:C154))</f>
         <v>116</v>
       </c>
-      <c r="B154" s="138"/>
+      <c r="B154" s="149"/>
       <c r="C154" s="35" t="s">
         <v>354</v>
       </c>
@@ -5477,7 +5477,7 @@
         <f>IF(LEN(C155)=0,"",COUNTA($C$34:C155))</f>
         <v>117</v>
       </c>
-      <c r="B155" s="138"/>
+      <c r="B155" s="149"/>
       <c r="C155" s="35" t="s">
         <v>355</v>
       </c>
@@ -5495,7 +5495,7 @@
         <f>IF(LEN(C156)=0,"",COUNTA($C$34:C156))</f>
         <v>118</v>
       </c>
-      <c r="B156" s="138"/>
+      <c r="B156" s="149"/>
       <c r="C156" s="35" t="s">
         <v>356</v>
       </c>
@@ -5513,7 +5513,7 @@
         <f>IF(LEN(C157)=0,"",COUNTA($C$34:C157))</f>
         <v>119</v>
       </c>
-      <c r="B157" s="138"/>
+      <c r="B157" s="149"/>
       <c r="C157" s="35" t="s">
         <v>357</v>
       </c>
@@ -5531,7 +5531,7 @@
         <f>IF(LEN(C158)=0,"",COUNTA($C$34:C158))</f>
         <v>120</v>
       </c>
-      <c r="B158" s="138"/>
+      <c r="B158" s="149"/>
       <c r="C158" s="35" t="s">
         <v>358</v>
       </c>
@@ -5549,7 +5549,7 @@
         <f>IF(LEN(C159)=0,"",COUNTA($C$34:C159))</f>
         <v>121</v>
       </c>
-      <c r="B159" s="138"/>
+      <c r="B159" s="149"/>
       <c r="C159" s="35" t="s">
         <v>359</v>
       </c>
@@ -5567,7 +5567,7 @@
         <f>IF(LEN(C160)=0,"",COUNTA($C$34:C160))</f>
         <v>122</v>
       </c>
-      <c r="B160" s="138"/>
+      <c r="B160" s="149"/>
       <c r="C160" s="35" t="s">
         <v>360</v>
       </c>
@@ -5585,7 +5585,7 @@
         <f>IF(LEN(C161)=0,"",COUNTA($C$34:C161))</f>
         <v>123</v>
       </c>
-      <c r="B161" s="138"/>
+      <c r="B161" s="149"/>
       <c r="C161" s="35" t="s">
         <v>361</v>
       </c>
@@ -5603,7 +5603,7 @@
         <f>IF(LEN(C162)=0,"",COUNTA($C$34:C162))</f>
         <v>124</v>
       </c>
-      <c r="B162" s="138"/>
+      <c r="B162" s="149"/>
       <c r="C162" s="35" t="s">
         <v>362</v>
       </c>
@@ -5621,7 +5621,7 @@
         <f>IF(LEN(C163)=0,"",COUNTA($C$34:C163))</f>
         <v>125</v>
       </c>
-      <c r="B163" s="138"/>
+      <c r="B163" s="149"/>
       <c r="C163" s="35" t="s">
         <v>363</v>
       </c>
@@ -5639,7 +5639,7 @@
         <f>IF(LEN(C164)=0,"",COUNTA($C$34:C164))</f>
         <v>126</v>
       </c>
-      <c r="B164" s="138"/>
+      <c r="B164" s="149"/>
       <c r="C164" s="35" t="s">
         <v>364</v>
       </c>
@@ -5655,7 +5655,7 @@
         <f>IF(LEN(C165)=0,"",COUNTA($C$34:C165))</f>
         <v>127</v>
       </c>
-      <c r="B165" s="138"/>
+      <c r="B165" s="149"/>
       <c r="C165" s="35" t="s">
         <v>365</v>
       </c>
@@ -5671,7 +5671,7 @@
         <f>IF(LEN(C166)=0,"",COUNTA($C$34:C166))</f>
         <v>128</v>
       </c>
-      <c r="B166" s="138"/>
+      <c r="B166" s="149"/>
       <c r="C166" s="35" t="s">
         <v>366</v>
       </c>
@@ -5689,7 +5689,7 @@
         <f>IF(LEN(C167)=0,"",COUNTA($C$34:C167))</f>
         <v>129</v>
       </c>
-      <c r="B167" s="138"/>
+      <c r="B167" s="149"/>
       <c r="C167" s="35" t="s">
         <v>367</v>
       </c>
@@ -5707,7 +5707,7 @@
         <f>IF(LEN(C168)=0,"",COUNTA($C$34:C168))</f>
         <v>130</v>
       </c>
-      <c r="B168" s="138"/>
+      <c r="B168" s="149"/>
       <c r="C168" s="35" t="s">
         <v>368</v>
       </c>
@@ -5720,12 +5720,12 @@
       <c r="F168" s="40"/>
       <c r="G168" s="12"/>
     </row>
-    <row r="169" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A169" s="37">
         <f>IF(LEN(C169)=0,"",COUNTA($C$34:C169))</f>
         <v>131</v>
       </c>
-      <c r="B169" s="138"/>
+      <c r="B169" s="149"/>
       <c r="C169" s="35" t="s">
         <v>369</v>
       </c>
@@ -5739,12 +5739,12 @@
       <c r="G169" s="12"/>
     </row>
     <row r="170" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="137" t="s">
+      <c r="A170" s="130" t="s">
         <v>206</v>
       </c>
-      <c r="B170" s="137"/>
-      <c r="C170" s="137"/>
-      <c r="D170" s="137"/>
+      <c r="B170" s="130"/>
+      <c r="C170" s="130"/>
+      <c r="D170" s="130"/>
       <c r="E170" s="77"/>
       <c r="F170" s="67"/>
       <c r="G170" s="12"/>
@@ -5809,7 +5809,7 @@
         <f>IF(LEN(C174)=0,"",COUNTA($C$34:C174))</f>
         <v>135</v>
       </c>
-      <c r="B174" s="139" t="s">
+      <c r="B174" s="146" t="s">
         <v>203</v>
       </c>
       <c r="C174" s="35" t="s">
@@ -5828,7 +5828,7 @@
         <f>IF(LEN(C175)=0,"",COUNTA($C$34:C175))</f>
         <v>136</v>
       </c>
-      <c r="B175" s="140"/>
+      <c r="B175" s="148"/>
       <c r="C175" s="35" t="s">
         <v>224</v>
       </c>
@@ -5841,12 +5841,12 @@
       <c r="F175" s="40"/>
     </row>
     <row r="176" spans="1:8" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="130" t="s">
+      <c r="A176" s="134" t="s">
         <v>163</v>
       </c>
-      <c r="B176" s="131"/>
-      <c r="C176" s="131"/>
-      <c r="D176" s="132"/>
+      <c r="B176" s="135"/>
+      <c r="C176" s="135"/>
+      <c r="D176" s="136"/>
       <c r="E176" s="120"/>
       <c r="F176" s="62"/>
     </row>
@@ -5865,7 +5865,7 @@
       <c r="E177" s="83">
         <v>71000</v>
       </c>
-      <c r="F177" s="141" t="s">
+      <c r="F177" s="128" t="s">
         <v>384</v>
       </c>
     </row>
@@ -5884,15 +5884,15 @@
       <c r="E178" s="83">
         <v>86000</v>
       </c>
-      <c r="F178" s="142"/>
+      <c r="F178" s="129"/>
     </row>
     <row r="179" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="137" t="s">
+      <c r="A179" s="130" t="s">
         <v>168</v>
       </c>
-      <c r="B179" s="137"/>
-      <c r="C179" s="137"/>
-      <c r="D179" s="137"/>
+      <c r="B179" s="130"/>
+      <c r="C179" s="130"/>
+      <c r="D179" s="130"/>
       <c r="E179" s="77"/>
       <c r="F179" s="67"/>
       <c r="G179" s="12"/>
@@ -5912,7 +5912,7 @@
       <c r="E180" s="106">
         <v>1968000</v>
       </c>
-      <c r="F180" s="134" t="s">
+      <c r="F180" s="131" t="s">
         <v>326</v>
       </c>
       <c r="G180" s="12"/>
@@ -5932,7 +5932,7 @@
       <c r="E181" s="106">
         <v>2952000</v>
       </c>
-      <c r="F181" s="135"/>
+      <c r="F181" s="132"/>
       <c r="G181" s="12"/>
     </row>
     <row r="182" spans="1:7" ht="66" x14ac:dyDescent="0.25">
@@ -5950,7 +5950,7 @@
       <c r="E182" s="106">
         <v>4100000</v>
       </c>
-      <c r="F182" s="136"/>
+      <c r="F182" s="133"/>
       <c r="G182" s="12"/>
     </row>
     <row r="183" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -6046,17 +6046,17 @@
       <c r="G187" s="12"/>
     </row>
     <row r="188" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A188" s="137" t="s">
+      <c r="A188" s="130" t="s">
         <v>263</v>
       </c>
-      <c r="B188" s="137"/>
-      <c r="C188" s="137"/>
-      <c r="D188" s="137"/>
+      <c r="B188" s="130"/>
+      <c r="C188" s="130"/>
+      <c r="D188" s="130"/>
       <c r="E188" s="77"/>
       <c r="F188" s="67"/>
       <c r="G188" s="12"/>
     </row>
-    <row r="189" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A189" s="37">
         <f>IF(LEN(C189)=0,"",COUNTA($C$34:C189))</f>
         <v>147</v>
@@ -6075,12 +6075,12 @@
       <c r="G189" s="12"/>
     </row>
     <row r="190" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="137" t="s">
+      <c r="A190" s="130" t="s">
         <v>233</v>
       </c>
-      <c r="B190" s="137"/>
-      <c r="C190" s="137"/>
-      <c r="D190" s="137"/>
+      <c r="B190" s="130"/>
+      <c r="C190" s="130"/>
+      <c r="D190" s="130"/>
       <c r="E190" s="77"/>
       <c r="F190" s="67"/>
       <c r="G190" s="12"/>
@@ -6266,12 +6266,12 @@
       <c r="G200" s="12"/>
     </row>
     <row r="201" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A201" s="130" t="s">
+      <c r="A201" s="134" t="s">
         <v>322</v>
       </c>
-      <c r="B201" s="131"/>
-      <c r="C201" s="131"/>
-      <c r="D201" s="132"/>
+      <c r="B201" s="135"/>
+      <c r="C201" s="135"/>
+      <c r="D201" s="136"/>
       <c r="E201" s="66"/>
       <c r="F201" s="67"/>
       <c r="G201" s="12"/>
@@ -6365,12 +6365,12 @@
       <c r="G206" s="12"/>
     </row>
     <row r="207" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="130" t="s">
+      <c r="A207" s="134" t="s">
         <v>221</v>
       </c>
-      <c r="B207" s="131"/>
-      <c r="C207" s="131"/>
-      <c r="D207" s="132"/>
+      <c r="B207" s="135"/>
+      <c r="C207" s="135"/>
+      <c r="D207" s="136"/>
       <c r="E207" s="66"/>
       <c r="F207" s="67"/>
       <c r="G207" s="12"/>
@@ -6430,12 +6430,12 @@
       <c r="G210" s="12"/>
     </row>
     <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="130" t="s">
+      <c r="A211" s="134" t="s">
         <v>210</v>
       </c>
-      <c r="B211" s="131"/>
-      <c r="C211" s="131"/>
-      <c r="D211" s="132"/>
+      <c r="B211" s="135"/>
+      <c r="C211" s="135"/>
+      <c r="D211" s="136"/>
       <c r="E211" s="66"/>
       <c r="F211" s="67"/>
       <c r="G211" s="12"/>
@@ -6450,7 +6450,7 @@
         <v>211</v>
       </c>
       <c r="D212" s="35"/>
-      <c r="E212" s="127">
+      <c r="E212" s="137">
         <v>183000</v>
       </c>
       <c r="F212" s="40"/>
@@ -6466,7 +6466,7 @@
         <v>212</v>
       </c>
       <c r="D213" s="35"/>
-      <c r="E213" s="128"/>
+      <c r="E213" s="138"/>
       <c r="F213" s="40"/>
       <c r="G213" s="12"/>
     </row>
@@ -6480,7 +6480,7 @@
         <v>213</v>
       </c>
       <c r="D214" s="35"/>
-      <c r="E214" s="128"/>
+      <c r="E214" s="138"/>
       <c r="F214" s="40"/>
       <c r="G214" s="12"/>
     </row>
@@ -6494,17 +6494,17 @@
         <v>214</v>
       </c>
       <c r="D215" s="35"/>
-      <c r="E215" s="129"/>
+      <c r="E215" s="139"/>
       <c r="F215" s="40"/>
       <c r="G215" s="12"/>
     </row>
     <row r="216" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="130" t="s">
+      <c r="A216" s="134" t="s">
         <v>413</v>
       </c>
-      <c r="B216" s="131"/>
-      <c r="C216" s="131"/>
-      <c r="D216" s="132"/>
+      <c r="B216" s="135"/>
+      <c r="C216" s="135"/>
+      <c r="D216" s="136"/>
       <c r="E216" s="66"/>
       <c r="F216" s="67"/>
       <c r="G216" s="12"/>
@@ -6582,12 +6582,12 @@
       <c r="F221" s="93"/>
     </row>
     <row r="222" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A222" s="133" t="s">
+      <c r="A222" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="B222" s="133"/>
-      <c r="C222" s="133"/>
-      <c r="D222" s="133"/>
+      <c r="B222" s="127"/>
+      <c r="C222" s="127"/>
+      <c r="D222" s="127"/>
       <c r="E222" s="26"/>
       <c r="F222" s="94"/>
     </row>
@@ -6705,57 +6705,6 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="B227:F227"/>
-    <mergeCell ref="A222:D222"/>
-    <mergeCell ref="F177:F178"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="F180:F182"/>
-    <mergeCell ref="A188:D188"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="A201:D201"/>
-    <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="E212:E215"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="A176:D176"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="B100:B113"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="B118:B126"/>
-    <mergeCell ref="B127:B132"/>
-    <mergeCell ref="B133:B139"/>
-    <mergeCell ref="B140:B169"/>
-    <mergeCell ref="A170:D170"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="B60:B72"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="B81:B88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="F46:F48"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="D1:F5"/>
     <mergeCell ref="A7:F7"/>
@@ -6770,6 +6719,57 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="B60:B72"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="B81:B88"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A176:D176"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="B100:B113"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="B118:B126"/>
+    <mergeCell ref="B127:B132"/>
+    <mergeCell ref="B133:B139"/>
+    <mergeCell ref="B140:B169"/>
+    <mergeCell ref="A170:D170"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="A222:D222"/>
+    <mergeCell ref="F177:F178"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="F180:F182"/>
+    <mergeCell ref="A188:D188"/>
+    <mergeCell ref="A190:D190"/>
+    <mergeCell ref="A201:D201"/>
+    <mergeCell ref="A207:D207"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="E212:E215"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="B227:F227"/>
   </mergeCells>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="60" fitToHeight="0" orientation="portrait" r:id="rId1"/>
